--- a/output/SPX_daily_20260721.xlsx
+++ b/output/SPX_daily_20260721.xlsx
@@ -1140,16 +1140,16 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Seagate Technology</t>
+          <t>Coherent Corp.</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>201.8</v>
+        <v>62.1</v>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
@@ -1158,12 +1158,12 @@
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+2.1</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>-16.6</t>
+          <t>-18.6</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="I15" s="18" t="n">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
       </c>
       <c r="K15" s="20" t="inlineStr">
         <is>
-          <t>Technology Hardware, Storage &amp; Peripherals 분야의 미국 상장 기업</t>
+          <t>Electronic Components 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -1196,16 +1196,16 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Coherent Corp.</t>
+          <t>Seagate Technology</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>62.1</v>
+        <v>201.8</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>+2.1</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>-18.6</t>
+          <t>-16.6</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -1228,7 +1228,7 @@
         </is>
       </c>
       <c r="I16" s="18" t="n">
-        <v>201</v>
+        <v>54</v>
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K16" s="20" t="inlineStr">
         <is>
-          <t>Electronic Components 분야의 미국 상장 기업</t>
+          <t>Technology Hardware, Storage &amp; Peripherals 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -2330,30 +2330,30 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="D37" s="25" t="n">
-        <v>34.9</v>
+        <v>11.3</v>
       </c>
       <c r="E37" s="26" t="inlineStr">
         <is>
           <t>-4.1</t>
         </is>
       </c>
-      <c r="F37" s="27" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="G37" s="27" t="inlineStr">
-        <is>
-          <t>+20.7</t>
+      <c r="F37" s="26" t="inlineStr">
+        <is>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="G37" s="26" t="inlineStr">
+        <is>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
@@ -2362,16 +2362,16 @@
         </is>
       </c>
       <c r="I37" s="29" t="n">
-        <v>289</v>
+        <v>479</v>
       </c>
       <c r="J37" s="30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K37" s="31" t="inlineStr">
         <is>
-          <t>Application Software 분야의 미국 상장 기업</t>
+          <t>Insurance Brokers 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L37" s="31" t="inlineStr">
@@ -2386,16 +2386,16 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>BLDR</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
-        <v>24.2</v>
+        <v>7.5</v>
       </c>
       <c r="E38" s="26" t="inlineStr">
         <is>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="F38" s="26" t="inlineStr">
         <is>
-          <t>-1.0</t>
-        </is>
-      </c>
-      <c r="G38" s="27" t="inlineStr">
-        <is>
-          <t>+0.6</t>
+          <t>-7.2</t>
+        </is>
+      </c>
+      <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>-13.5</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
@@ -2418,16 +2418,16 @@
         </is>
       </c>
       <c r="I38" s="29" t="n">
-        <v>359</v>
+        <v>502</v>
       </c>
       <c r="J38" s="30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K38" s="31" t="inlineStr">
         <is>
-          <t>Internet Services &amp; Infrastructure 분야의 미국 상장 기업</t>
+          <t>Building Products 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L38" s="31" t="inlineStr">
@@ -2442,16 +2442,16 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="D39" s="25" t="n">
-        <v>7.5</v>
+        <v>24.2</v>
       </c>
       <c r="E39" s="26" t="inlineStr">
         <is>
@@ -2460,12 +2460,12 @@
       </c>
       <c r="F39" s="26" t="inlineStr">
         <is>
-          <t>-7.2</t>
-        </is>
-      </c>
-      <c r="G39" s="26" t="inlineStr">
-        <is>
-          <t>-13.5</t>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="G39" s="27" t="inlineStr">
+        <is>
+          <t>+0.6</t>
         </is>
       </c>
       <c r="H39" s="28" t="inlineStr">
@@ -2474,16 +2474,16 @@
         </is>
       </c>
       <c r="I39" s="29" t="n">
-        <v>502</v>
+        <v>359</v>
       </c>
       <c r="J39" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K39" s="31" t="inlineStr">
         <is>
-          <t>Building Products 분야의 미국 상장 기업</t>
+          <t>Internet Services &amp; Infrastructure 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L39" s="31" t="inlineStr">
@@ -2554,30 +2554,30 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>11.3</v>
+        <v>34.9</v>
       </c>
       <c r="E41" s="26" t="inlineStr">
         <is>
           <t>-4.1</t>
         </is>
       </c>
-      <c r="F41" s="26" t="inlineStr">
-        <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="G41" s="26" t="inlineStr">
-        <is>
-          <t>-1.8</t>
+      <c r="F41" s="27" t="inlineStr">
+        <is>
+          <t>+1.0</t>
+        </is>
+      </c>
+      <c r="G41" s="27" t="inlineStr">
+        <is>
+          <t>+20.7</t>
         </is>
       </c>
       <c r="H41" s="28" t="inlineStr">
@@ -2586,16 +2586,16 @@
         </is>
       </c>
       <c r="I41" s="29" t="n">
-        <v>479</v>
+        <v>289</v>
       </c>
       <c r="J41" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K41" s="31" t="inlineStr">
         <is>
-          <t>Insurance Brokers 분야의 미국 상장 기업</t>
+          <t>Application Software 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L41" s="31" t="inlineStr">
@@ -2890,16 +2890,16 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>FactSet</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
-        <v>8.800000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="E47" s="26" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
       </c>
       <c r="F47" s="26" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="G47" s="27" t="inlineStr">
         <is>
-          <t>+11.6</t>
+          <t>+12.7</t>
         </is>
       </c>
       <c r="H47" s="28" t="inlineStr">
@@ -2922,16 +2922,16 @@
         </is>
       </c>
       <c r="I47" s="29" t="n">
-        <v>498</v>
+        <v>118</v>
       </c>
       <c r="J47" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="K47" s="31" t="inlineStr">
         <is>
-          <t>Financial Exchanges &amp; Data 분야의 미국 상장 기업</t>
+          <t>Human Resource &amp; Employment Services 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L47" s="31" t="inlineStr">
@@ -2946,16 +2946,16 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>FactSet</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>98.40000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
@@ -2964,12 +2964,12 @@
       </c>
       <c r="F48" s="26" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="G48" s="27" t="inlineStr">
         <is>
-          <t>+12.7</t>
+          <t>+11.6</t>
         </is>
       </c>
       <c r="H48" s="28" t="inlineStr">
@@ -2978,16 +2978,16 @@
         </is>
       </c>
       <c r="I48" s="29" t="n">
-        <v>118</v>
+        <v>498</v>
       </c>
       <c r="J48" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K48" s="31" t="inlineStr">
         <is>
-          <t>Human Resource &amp; Employment Services 분야의 미국 상장 기업</t>
+          <t>Financial Exchanges &amp; Data 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L48" s="31" t="inlineStr">
@@ -3002,16 +3002,16 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>22.6</v>
+        <v>45.6</v>
       </c>
       <c r="E49" s="26" t="inlineStr">
         <is>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="F49" s="26" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
         <is>
-          <t>+12.8</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="H49" s="28" t="inlineStr">
@@ -3034,16 +3034,16 @@
         </is>
       </c>
       <c r="I49" s="29" t="n">
-        <v>377</v>
+        <v>249</v>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="K49" s="31" t="inlineStr">
         <is>
-          <t>Insurance Brokers 분야의 미국 상장 기업</t>
+          <t>Consumer Electronics 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L49" s="31" t="inlineStr">
@@ -3058,30 +3058,30 @@
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>BRO</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
-        <v>35.4</v>
+        <v>22.6</v>
       </c>
       <c r="E50" s="26" t="inlineStr">
         <is>
           <t>-3.3</t>
         </is>
       </c>
-      <c r="F50" s="27" t="inlineStr">
-        <is>
-          <t>+1.2</t>
+      <c r="F50" s="26" t="inlineStr">
+        <is>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>+6.5</t>
+          <t>+12.8</t>
         </is>
       </c>
       <c r="H50" s="28" t="inlineStr">
@@ -3090,16 +3090,16 @@
         </is>
       </c>
       <c r="I50" s="29" t="n">
-        <v>287</v>
+        <v>377</v>
       </c>
       <c r="J50" s="30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="K50" s="31" t="inlineStr">
         <is>
-          <t>Electronic Equipment &amp; Instruments 분야의 미국 상장 기업</t>
+          <t>Insurance Brokers 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L50" s="31" t="inlineStr">
@@ -3114,30 +3114,30 @@
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
-        <v>45.6</v>
+        <v>35.4</v>
       </c>
       <c r="E51" s="26" t="inlineStr">
         <is>
           <t>-3.3</t>
         </is>
       </c>
-      <c r="F51" s="26" t="inlineStr">
-        <is>
-          <t>-2.0</t>
+      <c r="F51" s="27" t="inlineStr">
+        <is>
+          <t>+1.2</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+6.5</t>
         </is>
       </c>
       <c r="H51" s="28" t="inlineStr">
@@ -3146,16 +3146,16 @@
         </is>
       </c>
       <c r="I51" s="29" t="n">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="J51" s="30" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="K51" s="31" t="inlineStr">
         <is>
-          <t>Consumer Electronics 분야의 미국 상장 기업</t>
+          <t>Electronic Equipment &amp; Instruments 분야의 미국 상장 기업</t>
         </is>
       </c>
       <c r="L51" s="31" t="inlineStr">
@@ -3176,7 +3176,7 @@
         <is>
           <t>관측: 상승 225개·하락 266개로 상승 비율은 46%였습니다. 강세 섹터는 Information Technology +2.5%, Energy +1.2%, 약세 섹터는 Consumer Staples -1.1%, Communication Services -1.1%였습니다. 개별 종목 중 SNDK(+14.3%)가 가장 강했고, DHR(-11.0%)가 가장 약했습니다.
 해석: 지수 내부의 방향성이 분산된 장세로, 전체 지수보다 주도 섹터와 개별 종목의 차별화가 두드러졌습니다.
-유의: AI 요약은 제공된 Yahoo Finance 기업 설명·뉴스 헤드라인과 시장 데이터만 근거로 하며 투자 의견이 아닙니다.</t>
+유의: AI 요약은 제공된 Yahoo Finance 뉴스 헤드라인과 시장 데이터만 근거로 하며, 투자 조언이 아닙니다.</t>
         </is>
       </c>
     </row>

--- a/output/SPX_daily_20260721.xlsx
+++ b/output/SPX_daily_20260721.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="16">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,17 +79,8 @@
       <color rgb="00333333"/>
       <sz val="8"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <color rgb="00333333"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="10">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -124,16 +115,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E6EEFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EAF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -204,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -292,12 +273,6 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -664,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -955,16 +930,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr">
-        <is>
-          <t>Technology Hardware, Storage &amp; Peripherals 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K11" s="20" t="inlineStr"/>
+      <c r="L11" s="20" t="inlineStr"/>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="11" t="n">
@@ -1011,16 +978,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr">
-        <is>
-          <t>Technology Hardware, Storage &amp; Peripherals 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K12" s="20" t="inlineStr"/>
+      <c r="L12" s="20" t="inlineStr"/>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -1067,16 +1026,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K13" s="20" t="inlineStr">
-        <is>
-          <t>Semiconductors 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K13" s="20" t="inlineStr"/>
+      <c r="L13" s="20" t="inlineStr"/>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="11" t="n">
@@ -1123,16 +1074,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K14" s="20" t="inlineStr">
-        <is>
-          <t>Semiconductor Materials &amp; Equipment 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K14" s="20" t="inlineStr"/>
+      <c r="L14" s="20" t="inlineStr"/>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="11" t="n">
@@ -1179,16 +1122,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K15" s="20" t="inlineStr">
-        <is>
-          <t>Electronic Components 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L15" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K15" s="20" t="inlineStr"/>
+      <c r="L15" s="20" t="inlineStr"/>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="11" t="n">
@@ -1205,7 +1140,7 @@
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>201.8</v>
+        <v>200</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
@@ -1235,16 +1170,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K16" s="20" t="inlineStr">
-        <is>
-          <t>Technology Hardware, Storage &amp; Peripherals 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K16" s="20" t="inlineStr"/>
+      <c r="L16" s="20" t="inlineStr"/>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="11" t="n">
@@ -1291,16 +1218,8 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="K17" s="20" t="inlineStr">
-        <is>
-          <t>Financial Exchanges &amp; Data 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L17" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K17" s="20" t="inlineStr"/>
+      <c r="L17" s="20" t="inlineStr"/>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="11" t="n">
@@ -1347,16 +1266,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr">
-        <is>
-          <t>Communications Equipment 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K18" s="20" t="inlineStr"/>
+      <c r="L18" s="20" t="inlineStr"/>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="11" t="n">
@@ -1403,16 +1314,8 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="K19" s="20" t="inlineStr">
-        <is>
-          <t>Leisure Products 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K19" s="20" t="inlineStr"/>
+      <c r="L19" s="20" t="inlineStr"/>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="11" t="n">
@@ -1459,16 +1362,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K20" s="20" t="inlineStr">
-        <is>
-          <t>Semiconductors 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L20" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K20" s="20" t="inlineStr"/>
+      <c r="L20" s="20" t="inlineStr"/>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="11" t="n">
@@ -1515,16 +1410,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K21" s="20" t="inlineStr">
-        <is>
-          <t>Semiconductors 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L21" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K21" s="20" t="inlineStr"/>
+      <c r="L21" s="20" t="inlineStr"/>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="11" t="n">
@@ -1571,16 +1458,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K22" s="20" t="inlineStr">
-        <is>
-          <t>Communications Equipment 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L22" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K22" s="20" t="inlineStr"/>
+      <c r="L22" s="20" t="inlineStr"/>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="11" t="n">
@@ -1627,16 +1506,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K23" s="20" t="inlineStr">
-        <is>
-          <t>Semiconductor Materials &amp; Equipment 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K23" s="20" t="inlineStr"/>
+      <c r="L23" s="20" t="inlineStr"/>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="11" t="n">
@@ -1653,7 +1524,7 @@
         </is>
       </c>
       <c r="D24" s="14" t="n">
-        <v>89.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="E24" s="15" t="inlineStr">
         <is>
@@ -1683,16 +1554,8 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr">
-        <is>
-          <t>Industrial Conglomerates 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K24" s="20" t="inlineStr"/>
+      <c r="L24" s="20" t="inlineStr"/>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="11" t="n">
@@ -1739,16 +1602,8 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="K25" s="20" t="inlineStr">
-        <is>
-          <t>Investment Banking &amp; Brokerage 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K25" s="20" t="inlineStr"/>
+      <c r="L25" s="20" t="inlineStr"/>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="11" t="n">
@@ -1788,23 +1643,15 @@
         </is>
       </c>
       <c r="I26" s="18" t="n">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K26" s="20" t="inlineStr">
-        <is>
-          <t>Technology Hardware, Storage &amp; Peripherals 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K26" s="20" t="inlineStr"/>
+      <c r="L26" s="20" t="inlineStr"/>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="11" t="n">
@@ -1851,16 +1698,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K27" s="20" t="inlineStr">
-        <is>
-          <t>Semiconductors 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K27" s="20" t="inlineStr"/>
+      <c r="L27" s="20" t="inlineStr"/>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="11" t="n">
@@ -1907,16 +1746,8 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="K28" s="20" t="inlineStr">
-        <is>
-          <t>Copper 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L28" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K28" s="20" t="inlineStr"/>
+      <c r="L28" s="20" t="inlineStr"/>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="11" t="n">
@@ -1963,16 +1794,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K29" s="20" t="inlineStr">
-        <is>
-          <t>Electronic Manufacturing Services 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K29" s="20" t="inlineStr"/>
+      <c r="L29" s="20" t="inlineStr"/>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="11" t="n">
@@ -2019,16 +1842,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K30" s="20" t="inlineStr">
-        <is>
-          <t>Electronic Components 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L30" s="20" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K30" s="20" t="inlineStr"/>
+      <c r="L30" s="20" t="inlineStr"/>
     </row>
     <row r="31" ht="4" customHeight="1">
       <c r="A31" s="21" t="n"/>
@@ -2059,7 +1874,7 @@
         </is>
       </c>
       <c r="D32" s="25" t="n">
-        <v>126.7</v>
+        <v>125.8</v>
       </c>
       <c r="E32" s="26" t="inlineStr">
         <is>
@@ -2089,16 +1904,8 @@
           <t>Health Care</t>
         </is>
       </c>
-      <c r="K32" s="31" t="inlineStr">
-        <is>
-          <t>Life Sciences Tools &amp; Services 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L32" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K32" s="31" t="inlineStr"/>
+      <c r="L32" s="31" t="inlineStr"/>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="22" t="n">
@@ -2115,7 +1922,7 @@
         </is>
       </c>
       <c r="D33" s="25" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="E33" s="26" t="inlineStr">
         <is>
@@ -2145,16 +1952,8 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="K33" s="31" t="inlineStr">
-        <is>
-          <t>Financial Exchanges &amp; Data 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L33" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K33" s="31" t="inlineStr"/>
+      <c r="L33" s="31" t="inlineStr"/>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="22" t="n">
@@ -2201,16 +2000,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K34" s="31" t="inlineStr">
-        <is>
-          <t>Application Software 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L34" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K34" s="31" t="inlineStr"/>
+      <c r="L34" s="31" t="inlineStr"/>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="22" t="n">
@@ -2257,16 +2048,8 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="K35" s="31" t="inlineStr">
-        <is>
-          <t>Oil &amp; Gas Equipment &amp; Services 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L35" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K35" s="31" t="inlineStr"/>
+      <c r="L35" s="31" t="inlineStr"/>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="22" t="n">
@@ -2313,16 +2096,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K36" s="31" t="inlineStr">
-        <is>
-          <t>IT Consulting &amp; Other Services 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L36" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K36" s="31" t="inlineStr"/>
+      <c r="L36" s="31" t="inlineStr"/>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="22" t="n">
@@ -2330,16 +2105,16 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="D37" s="25" t="n">
-        <v>11.3</v>
+        <v>24.2</v>
       </c>
       <c r="E37" s="26" t="inlineStr">
         <is>
@@ -2348,12 +2123,12 @@
       </c>
       <c r="F37" s="26" t="inlineStr">
         <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="G37" s="26" t="inlineStr">
-        <is>
-          <t>-1.8</t>
+          <t>-1.0</t>
+        </is>
+      </c>
+      <c r="G37" s="27" t="inlineStr">
+        <is>
+          <t>+0.6</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
@@ -2362,23 +2137,15 @@
         </is>
       </c>
       <c r="I37" s="29" t="n">
-        <v>479</v>
+        <v>358</v>
       </c>
       <c r="J37" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="K37" s="31" t="inlineStr">
-        <is>
-          <t>Insurance Brokers 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L37" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="K37" s="31" t="inlineStr"/>
+      <c r="L37" s="31" t="inlineStr"/>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="22" t="n">
@@ -2386,16 +2153,16 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
-        <v>7.5</v>
+        <v>30.7</v>
       </c>
       <c r="E38" s="26" t="inlineStr">
         <is>
@@ -2404,12 +2171,12 @@
       </c>
       <c r="F38" s="26" t="inlineStr">
         <is>
-          <t>-7.2</t>
-        </is>
-      </c>
-      <c r="G38" s="26" t="inlineStr">
-        <is>
-          <t>-13.5</t>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="G38" s="27" t="inlineStr">
+        <is>
+          <t>+23.4</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
@@ -2418,23 +2185,15 @@
         </is>
       </c>
       <c r="I38" s="29" t="n">
-        <v>502</v>
+        <v>307</v>
       </c>
       <c r="J38" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K38" s="31" t="inlineStr">
-        <is>
-          <t>Building Products 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L38" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="K38" s="31" t="inlineStr"/>
+      <c r="L38" s="31" t="inlineStr"/>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="22" t="n">
@@ -2442,30 +2201,30 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="D39" s="25" t="n">
-        <v>24.2</v>
+        <v>34.9</v>
       </c>
       <c r="E39" s="26" t="inlineStr">
         <is>
           <t>-4.1</t>
         </is>
       </c>
-      <c r="F39" s="26" t="inlineStr">
-        <is>
-          <t>-1.0</t>
+      <c r="F39" s="27" t="inlineStr">
+        <is>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="G39" s="27" t="inlineStr">
         <is>
-          <t>+0.6</t>
+          <t>+20.7</t>
         </is>
       </c>
       <c r="H39" s="28" t="inlineStr">
@@ -2474,23 +2233,15 @@
         </is>
       </c>
       <c r="I39" s="29" t="n">
-        <v>359</v>
+        <v>289</v>
       </c>
       <c r="J39" s="30" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K39" s="31" t="inlineStr">
-        <is>
-          <t>Internet Services &amp; Infrastructure 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L39" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K39" s="31" t="inlineStr"/>
+      <c r="L39" s="31" t="inlineStr"/>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="22" t="n">
@@ -2498,16 +2249,16 @@
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
-        <v>30.7</v>
+        <v>11.3</v>
       </c>
       <c r="E40" s="26" t="inlineStr">
         <is>
@@ -2516,12 +2267,12 @@
       </c>
       <c r="F40" s="26" t="inlineStr">
         <is>
-          <t>-2.0</t>
-        </is>
-      </c>
-      <c r="G40" s="27" t="inlineStr">
-        <is>
-          <t>+23.4</t>
+          <t>-9.5</t>
+        </is>
+      </c>
+      <c r="G40" s="26" t="inlineStr">
+        <is>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="H40" s="28" t="inlineStr">
@@ -2530,23 +2281,15 @@
         </is>
       </c>
       <c r="I40" s="29" t="n">
-        <v>307</v>
+        <v>479</v>
       </c>
       <c r="J40" s="30" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="K40" s="31" t="inlineStr">
-        <is>
-          <t>Health Care Technology 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L40" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="K40" s="31" t="inlineStr"/>
+      <c r="L40" s="31" t="inlineStr"/>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="22" t="n">
@@ -2554,30 +2297,30 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>BLDR</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>34.9</v>
+        <v>7.5</v>
       </c>
       <c r="E41" s="26" t="inlineStr">
         <is>
           <t>-4.1</t>
         </is>
       </c>
-      <c r="F41" s="27" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="G41" s="27" t="inlineStr">
-        <is>
-          <t>+20.7</t>
+      <c r="F41" s="26" t="inlineStr">
+        <is>
+          <t>-7.2</t>
+        </is>
+      </c>
+      <c r="G41" s="26" t="inlineStr">
+        <is>
+          <t>-13.5</t>
         </is>
       </c>
       <c r="H41" s="28" t="inlineStr">
@@ -2586,23 +2329,15 @@
         </is>
       </c>
       <c r="I41" s="29" t="n">
-        <v>289</v>
+        <v>502</v>
       </c>
       <c r="J41" s="30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="K41" s="31" t="inlineStr">
-        <is>
-          <t>Application Software 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L41" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K41" s="31" t="inlineStr"/>
+      <c r="L41" s="31" t="inlineStr"/>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="22" t="n">
@@ -2649,16 +2384,8 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="K42" s="31" t="inlineStr">
-        <is>
-          <t>Real Estate Services 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L42" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K42" s="31" t="inlineStr"/>
+      <c r="L42" s="31" t="inlineStr"/>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="22" t="n">
@@ -2675,7 +2402,7 @@
         </is>
       </c>
       <c r="D43" s="25" t="n">
-        <v>20.9</v>
+        <v>20.3</v>
       </c>
       <c r="E43" s="26" t="inlineStr">
         <is>
@@ -2698,23 +2425,15 @@
         </is>
       </c>
       <c r="I43" s="29" t="n">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J43" s="30" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
-      <c r="K43" s="31" t="inlineStr">
-        <is>
-          <t>Research &amp; Consulting Services 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L43" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K43" s="31" t="inlineStr"/>
+      <c r="L43" s="31" t="inlineStr"/>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="22" t="n">
@@ -2722,16 +2441,16 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>Omnicom Group</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
-        <v>22.6</v>
+        <v>127.7</v>
       </c>
       <c r="E44" s="26" t="inlineStr">
         <is>
@@ -2740,12 +2459,12 @@
       </c>
       <c r="F44" s="26" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="G44" s="27" t="inlineStr">
         <is>
-          <t>+11.0</t>
+          <t>+10.9</t>
         </is>
       </c>
       <c r="H44" s="28" t="inlineStr">
@@ -2754,23 +2473,15 @@
         </is>
       </c>
       <c r="I44" s="29" t="n">
-        <v>379</v>
+        <v>91</v>
       </c>
       <c r="J44" s="30" t="inlineStr">
         <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="K44" s="31" t="inlineStr">
-        <is>
-          <t>Advertising 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L44" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="K44" s="31" t="inlineStr"/>
+      <c r="L44" s="31" t="inlineStr"/>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="22" t="n">
@@ -2778,16 +2489,16 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Omnicom Group</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
-        <v>127.7</v>
+        <v>22.6</v>
       </c>
       <c r="E45" s="26" t="inlineStr">
         <is>
@@ -2796,12 +2507,12 @@
       </c>
       <c r="F45" s="26" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
         <is>
-          <t>+10.9</t>
+          <t>+11.0</t>
         </is>
       </c>
       <c r="H45" s="28" t="inlineStr">
@@ -2810,23 +2521,15 @@
         </is>
       </c>
       <c r="I45" s="29" t="n">
-        <v>91</v>
+        <v>379</v>
       </c>
       <c r="J45" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="K45" s="31" t="inlineStr">
-        <is>
-          <t>Financial Exchanges &amp; Data 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L45" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="K45" s="31" t="inlineStr"/>
+      <c r="L45" s="31" t="inlineStr"/>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="22" t="n">
@@ -2873,16 +2576,8 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K46" s="31" t="inlineStr">
-        <is>
-          <t>Systems Software 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L46" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K46" s="31" t="inlineStr"/>
+      <c r="L46" s="31" t="inlineStr"/>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="22" t="n">
@@ -2929,16 +2624,8 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="K47" s="31" t="inlineStr">
-        <is>
-          <t>Human Resource &amp; Employment Services 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L47" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K47" s="31" t="inlineStr"/>
+      <c r="L47" s="31" t="inlineStr"/>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="22" t="n">
@@ -2985,16 +2672,8 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="K48" s="31" t="inlineStr">
-        <is>
-          <t>Financial Exchanges &amp; Data 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L48" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K48" s="31" t="inlineStr"/>
+      <c r="L48" s="31" t="inlineStr"/>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="22" t="n">
@@ -3002,16 +2681,16 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Broadridge Financial Solutions</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>45.6</v>
+        <v>16.8</v>
       </c>
       <c r="E49" s="26" t="inlineStr">
         <is>
@@ -3020,12 +2699,12 @@
       </c>
       <c r="F49" s="26" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+5.4</t>
         </is>
       </c>
       <c r="H49" s="28" t="inlineStr">
@@ -3034,23 +2713,15 @@
         </is>
       </c>
       <c r="I49" s="29" t="n">
-        <v>249</v>
+        <v>425</v>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="K49" s="31" t="inlineStr">
-        <is>
-          <t>Consumer Electronics 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L49" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K49" s="31" t="inlineStr"/>
+      <c r="L49" s="31" t="inlineStr"/>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="22" t="n">
@@ -3097,16 +2768,8 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="K50" s="31" t="inlineStr">
-        <is>
-          <t>Insurance Brokers 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L50" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
+      <c r="K50" s="31" t="inlineStr"/>
+      <c r="L50" s="31" t="inlineStr"/>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="22" t="n">
@@ -3114,30 +2777,30 @@
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>ROP</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
-        <v>35.4</v>
+        <v>45.6</v>
       </c>
       <c r="E51" s="26" t="inlineStr">
         <is>
           <t>-3.3</t>
         </is>
       </c>
-      <c r="F51" s="27" t="inlineStr">
-        <is>
-          <t>+1.2</t>
+      <c r="F51" s="26" t="inlineStr">
+        <is>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
-          <t>+6.5</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="H51" s="28" t="inlineStr">
@@ -3146,51 +2809,23 @@
         </is>
       </c>
       <c r="I51" s="29" t="n">
-        <v>287</v>
+        <v>249</v>
       </c>
       <c r="J51" s="30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="K51" s="31" t="inlineStr">
-        <is>
-          <t>Electronic Equipment &amp; Instruments 분야의 미국 상장 기업</t>
-        </is>
-      </c>
-      <c r="L51" s="31" t="inlineStr">
-        <is>
-          <t>당일 뉴스·공시 근거를 확인하지 못했습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="32" t="inlineStr">
-        <is>
-          <t>📈 금일 시황 요약 — 상승·하락 종목이 엇갈린 혼조 흐름</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="58" customHeight="1">
-      <c r="A55" s="33" t="inlineStr">
-        <is>
-          <t>관측: 상승 225개·하락 266개로 상승 비율은 46%였습니다. 강세 섹터는 Information Technology +2.5%, Energy +1.2%, 약세 섹터는 Consumer Staples -1.1%, Communication Services -1.1%였습니다. 개별 종목 중 SNDK(+14.3%)가 가장 강했고, DHR(-11.0%)가 가장 약했습니다.
-해석: 지수 내부의 방향성이 분산된 장세로, 전체 지수보다 주도 섹터와 개별 종목의 차별화가 두드러졌습니다.
-유의: AI 요약은 제공된 Yahoo Finance 뉴스 헤드라인과 시장 데이터만 근거로 하며, 투자 조언이 아닙니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="K51" s="31" t="inlineStr"/>
+      <c r="L51" s="31" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="12">
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B9:B10"/>
-    <mergeCell ref="A54:L54"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="I9:I10"/>
-    <mergeCell ref="A55:L57"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="J9:J10"/>

--- a/output/SPX_daily_20260721.xlsx
+++ b/output/SPX_daily_20260721.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +79,17 @@
       <color rgb="00333333"/>
       <sz val="8"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <color rgb="00333333"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -115,6 +124,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E6EEFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -185,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -273,6 +292,12 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -639,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -930,8 +955,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K11" s="20" t="inlineStr"/>
-      <c r="L11" s="20" t="inlineStr"/>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="11" t="n">
@@ -978,8 +1011,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K12" s="20" t="inlineStr"/>
-      <c r="L12" s="20" t="inlineStr"/>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="42" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -1026,8 +1067,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K13" s="20" t="inlineStr"/>
-      <c r="L13" s="20" t="inlineStr"/>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="42" customHeight="1">
       <c r="A14" s="11" t="n">
@@ -1074,8 +1123,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K14" s="20" t="inlineStr"/>
-      <c r="L14" s="20" t="inlineStr"/>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="42" customHeight="1">
       <c r="A15" s="11" t="n">
@@ -1083,16 +1140,16 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>COHR</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Coherent Corp.</t>
+          <t>Seagate Technology</t>
         </is>
       </c>
       <c r="D15" s="14" t="n">
-        <v>62.1</v>
+        <v>201.8</v>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
@@ -1101,12 +1158,12 @@
       </c>
       <c r="F15" s="15" t="inlineStr">
         <is>
-          <t>+2.1</t>
+          <t>+1.5</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
         <is>
-          <t>-18.6</t>
+          <t>-16.6</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -1115,15 +1172,23 @@
         </is>
       </c>
       <c r="I15" s="18" t="n">
-        <v>201</v>
+        <v>54</v>
       </c>
       <c r="J15" s="19" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K15" s="20" t="inlineStr"/>
-      <c r="L15" s="20" t="inlineStr"/>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="42" customHeight="1">
       <c r="A16" s="11" t="n">
@@ -1131,16 +1196,16 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>COHR</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>Seagate Technology</t>
+          <t>Coherent Corp.</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
-        <v>200</v>
+        <v>62.1</v>
       </c>
       <c r="E16" s="15" t="inlineStr">
         <is>
@@ -1149,12 +1214,12 @@
       </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
-          <t>+1.5</t>
+          <t>+2.1</t>
         </is>
       </c>
       <c r="G16" s="16" t="inlineStr">
         <is>
-          <t>-16.6</t>
+          <t>-18.6</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -1163,15 +1228,23 @@
         </is>
       </c>
       <c r="I16" s="18" t="n">
-        <v>54</v>
+        <v>201</v>
       </c>
       <c r="J16" s="19" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K16" s="20" t="inlineStr"/>
-      <c r="L16" s="20" t="inlineStr"/>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="42" customHeight="1">
       <c r="A17" s="11" t="n">
@@ -1218,8 +1291,16 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="K17" s="20" t="inlineStr"/>
-      <c r="L17" s="20" t="inlineStr"/>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>금융 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="42" customHeight="1">
       <c r="A18" s="11" t="n">
@@ -1266,8 +1347,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K18" s="20" t="inlineStr"/>
-      <c r="L18" s="20" t="inlineStr"/>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="42" customHeight="1">
       <c r="A19" s="11" t="n">
@@ -1314,8 +1403,16 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="K19" s="20" t="inlineStr"/>
-      <c r="L19" s="20" t="inlineStr"/>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>소비재·자동차·레저 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="42" customHeight="1">
       <c r="A20" s="11" t="n">
@@ -1362,8 +1459,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K20" s="20" t="inlineStr"/>
-      <c r="L20" s="20" t="inlineStr"/>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="42" customHeight="1">
       <c r="A21" s="11" t="n">
@@ -1410,8 +1515,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K21" s="20" t="inlineStr"/>
-      <c r="L21" s="20" t="inlineStr"/>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="11" t="n">
@@ -1458,8 +1571,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K22" s="20" t="inlineStr"/>
-      <c r="L22" s="20" t="inlineStr"/>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="42" customHeight="1">
       <c r="A23" s="11" t="n">
@@ -1506,8 +1627,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K23" s="20" t="inlineStr"/>
-      <c r="L23" s="20" t="inlineStr"/>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="42" customHeight="1">
       <c r="A24" s="11" t="n">
@@ -1554,8 +1683,16 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="K24" s="20" t="inlineStr"/>
-      <c r="L24" s="20" t="inlineStr"/>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>산업재·운송·방산 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="42" customHeight="1">
       <c r="A25" s="11" t="n">
@@ -1602,8 +1739,16 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="K25" s="20" t="inlineStr"/>
-      <c r="L25" s="20" t="inlineStr"/>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>금융 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="42" customHeight="1">
       <c r="A26" s="11" t="n">
@@ -1650,8 +1795,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K26" s="20" t="inlineStr"/>
-      <c r="L26" s="20" t="inlineStr"/>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="42" customHeight="1">
       <c r="A27" s="11" t="n">
@@ -1698,8 +1851,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K27" s="20" t="inlineStr"/>
-      <c r="L27" s="20" t="inlineStr"/>
+      <c r="K27" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="42" customHeight="1">
       <c r="A28" s="11" t="n">
@@ -1746,8 +1907,16 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="K28" s="20" t="inlineStr"/>
-      <c r="L28" s="20" t="inlineStr"/>
+      <c r="K28" s="20" t="inlineStr">
+        <is>
+          <t>소재 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="42" customHeight="1">
       <c r="A29" s="11" t="n">
@@ -1794,8 +1963,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K29" s="20" t="inlineStr"/>
-      <c r="L29" s="20" t="inlineStr"/>
+      <c r="K29" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="42" customHeight="1">
       <c r="A30" s="11" t="n">
@@ -1842,8 +2019,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K30" s="20" t="inlineStr"/>
-      <c r="L30" s="20" t="inlineStr"/>
+      <c r="K30" s="20" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="4" customHeight="1">
       <c r="A31" s="21" t="n"/>
@@ -1904,8 +2089,16 @@
           <t>Health Care</t>
         </is>
       </c>
-      <c r="K32" s="31" t="inlineStr"/>
-      <c r="L32" s="31" t="inlineStr"/>
+      <c r="K32" s="31" t="inlineStr">
+        <is>
+          <t>헬스케어·바이오 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L32" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="42" customHeight="1">
       <c r="A33" s="22" t="n">
@@ -1952,8 +2145,16 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="K33" s="31" t="inlineStr"/>
-      <c r="L33" s="31" t="inlineStr"/>
+      <c r="K33" s="31" t="inlineStr">
+        <is>
+          <t>금융 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L33" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="42" customHeight="1">
       <c r="A34" s="22" t="n">
@@ -2000,8 +2201,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K34" s="31" t="inlineStr"/>
-      <c r="L34" s="31" t="inlineStr"/>
+      <c r="K34" s="31" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L34" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="42" customHeight="1">
       <c r="A35" s="22" t="n">
@@ -2048,8 +2257,16 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="K35" s="31" t="inlineStr"/>
-      <c r="L35" s="31" t="inlineStr"/>
+      <c r="K35" s="31" t="inlineStr">
+        <is>
+          <t>에너지 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L35" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="42" customHeight="1">
       <c r="A36" s="22" t="n">
@@ -2096,8 +2313,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K36" s="31" t="inlineStr"/>
-      <c r="L36" s="31" t="inlineStr"/>
+      <c r="K36" s="31" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L36" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="42" customHeight="1">
       <c r="A37" s="22" t="n">
@@ -2105,30 +2330,30 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>VRSN</t>
+          <t>WDAY</t>
         </is>
       </c>
       <c r="C37" s="24" t="inlineStr">
         <is>
-          <t>Verisign</t>
+          <t>Workday, Inc.</t>
         </is>
       </c>
       <c r="D37" s="25" t="n">
-        <v>24.2</v>
+        <v>34.9</v>
       </c>
       <c r="E37" s="26" t="inlineStr">
         <is>
           <t>-4.1</t>
         </is>
       </c>
-      <c r="F37" s="26" t="inlineStr">
-        <is>
-          <t>-1.0</t>
+      <c r="F37" s="27" t="inlineStr">
+        <is>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="G37" s="27" t="inlineStr">
         <is>
-          <t>+0.6</t>
+          <t>+20.7</t>
         </is>
       </c>
       <c r="H37" s="28" t="inlineStr">
@@ -2137,15 +2362,23 @@
         </is>
       </c>
       <c r="I37" s="29" t="n">
-        <v>358</v>
+        <v>289</v>
       </c>
       <c r="J37" s="30" t="inlineStr">
         <is>
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K37" s="31" t="inlineStr"/>
-      <c r="L37" s="31" t="inlineStr"/>
+      <c r="K37" s="31" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L37" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="42" customHeight="1">
       <c r="A38" s="22" t="n">
@@ -2153,16 +2386,16 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>VEEV</t>
+          <t>VRSN</t>
         </is>
       </c>
       <c r="C38" s="24" t="inlineStr">
         <is>
-          <t>Veeva Systems</t>
+          <t>Verisign</t>
         </is>
       </c>
       <c r="D38" s="25" t="n">
-        <v>30.7</v>
+        <v>24.2</v>
       </c>
       <c r="E38" s="26" t="inlineStr">
         <is>
@@ -2171,12 +2404,12 @@
       </c>
       <c r="F38" s="26" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="G38" s="27" t="inlineStr">
         <is>
-          <t>+23.4</t>
+          <t>+0.6</t>
         </is>
       </c>
       <c r="H38" s="28" t="inlineStr">
@@ -2185,15 +2418,23 @@
         </is>
       </c>
       <c r="I38" s="29" t="n">
-        <v>307</v>
+        <v>358</v>
       </c>
       <c r="J38" s="30" t="inlineStr">
         <is>
-          <t>Health Care</t>
-        </is>
-      </c>
-      <c r="K38" s="31" t="inlineStr"/>
-      <c r="L38" s="31" t="inlineStr"/>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="K38" s="31" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L38" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="22" t="n">
@@ -2201,30 +2442,30 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>WDAY</t>
+          <t>BLDR</t>
         </is>
       </c>
       <c r="C39" s="24" t="inlineStr">
         <is>
-          <t>Workday, Inc.</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="D39" s="25" t="n">
-        <v>34.9</v>
+        <v>7.5</v>
       </c>
       <c r="E39" s="26" t="inlineStr">
         <is>
           <t>-4.1</t>
         </is>
       </c>
-      <c r="F39" s="27" t="inlineStr">
-        <is>
-          <t>+1.0</t>
-        </is>
-      </c>
-      <c r="G39" s="27" t="inlineStr">
-        <is>
-          <t>+20.7</t>
+      <c r="F39" s="26" t="inlineStr">
+        <is>
+          <t>-7.2</t>
+        </is>
+      </c>
+      <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>-13.5</t>
         </is>
       </c>
       <c r="H39" s="28" t="inlineStr">
@@ -2233,15 +2474,23 @@
         </is>
       </c>
       <c r="I39" s="29" t="n">
-        <v>289</v>
+        <v>502</v>
       </c>
       <c r="J39" s="30" t="inlineStr">
         <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="K39" s="31" t="inlineStr"/>
-      <c r="L39" s="31" t="inlineStr"/>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K39" s="31" t="inlineStr">
+        <is>
+          <t>산업재·운송·방산 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L39" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="42" customHeight="1">
       <c r="A40" s="22" t="n">
@@ -2249,16 +2498,16 @@
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>VEEV</t>
         </is>
       </c>
       <c r="C40" s="24" t="inlineStr">
         <is>
-          <t>Erie Indemnity</t>
+          <t>Veeva Systems</t>
         </is>
       </c>
       <c r="D40" s="25" t="n">
-        <v>11.3</v>
+        <v>30.7</v>
       </c>
       <c r="E40" s="26" t="inlineStr">
         <is>
@@ -2267,12 +2516,12 @@
       </c>
       <c r="F40" s="26" t="inlineStr">
         <is>
-          <t>-9.5</t>
-        </is>
-      </c>
-      <c r="G40" s="26" t="inlineStr">
-        <is>
-          <t>-1.8</t>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="G40" s="27" t="inlineStr">
+        <is>
+          <t>+23.4</t>
         </is>
       </c>
       <c r="H40" s="28" t="inlineStr">
@@ -2281,15 +2530,23 @@
         </is>
       </c>
       <c r="I40" s="29" t="n">
-        <v>479</v>
+        <v>307</v>
       </c>
       <c r="J40" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="K40" s="31" t="inlineStr"/>
-      <c r="L40" s="31" t="inlineStr"/>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="K40" s="31" t="inlineStr">
+        <is>
+          <t>헬스케어·바이오 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L40" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="22" t="n">
@@ -2297,16 +2554,16 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>BLDR</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="C41" s="24" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Erie Indemnity</t>
         </is>
       </c>
       <c r="D41" s="25" t="n">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="E41" s="26" t="inlineStr">
         <is>
@@ -2315,12 +2572,12 @@
       </c>
       <c r="F41" s="26" t="inlineStr">
         <is>
-          <t>-7.2</t>
+          <t>-9.5</t>
         </is>
       </c>
       <c r="G41" s="26" t="inlineStr">
         <is>
-          <t>-13.5</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="H41" s="28" t="inlineStr">
@@ -2329,15 +2586,23 @@
         </is>
       </c>
       <c r="I41" s="29" t="n">
-        <v>502</v>
+        <v>479</v>
       </c>
       <c r="J41" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K41" s="31" t="inlineStr"/>
-      <c r="L41" s="31" t="inlineStr"/>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="K41" s="31" t="inlineStr">
+        <is>
+          <t>금융 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L41" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="22" t="n">
@@ -2384,8 +2649,16 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="K42" s="31" t="inlineStr"/>
-      <c r="L42" s="31" t="inlineStr"/>
+      <c r="K42" s="31" t="inlineStr">
+        <is>
+          <t>부동산 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L42" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="42" customHeight="1">
       <c r="A43" s="22" t="n">
@@ -2432,8 +2705,16 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="K43" s="31" t="inlineStr"/>
-      <c r="L43" s="31" t="inlineStr"/>
+      <c r="K43" s="31" t="inlineStr">
+        <is>
+          <t>산업재·운송·방산 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L43" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="22" t="n">
@@ -2441,16 +2722,16 @@
       </c>
       <c r="B44" s="23" t="inlineStr">
         <is>
-          <t>SPGI</t>
+          <t>OMC</t>
         </is>
       </c>
       <c r="C44" s="24" t="inlineStr">
         <is>
-          <t>S&amp;P Global</t>
+          <t>Omnicom Group</t>
         </is>
       </c>
       <c r="D44" s="25" t="n">
-        <v>127.7</v>
+        <v>22.6</v>
       </c>
       <c r="E44" s="26" t="inlineStr">
         <is>
@@ -2459,12 +2740,12 @@
       </c>
       <c r="F44" s="26" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.9</t>
         </is>
       </c>
       <c r="G44" s="27" t="inlineStr">
         <is>
-          <t>+10.9</t>
+          <t>+11.0</t>
         </is>
       </c>
       <c r="H44" s="28" t="inlineStr">
@@ -2473,15 +2754,23 @@
         </is>
       </c>
       <c r="I44" s="29" t="n">
-        <v>91</v>
+        <v>379</v>
       </c>
       <c r="J44" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="K44" s="31" t="inlineStr"/>
-      <c r="L44" s="31" t="inlineStr"/>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="K44" s="31" t="inlineStr">
+        <is>
+          <t>통신·미디어·인터넷 서비스 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L44" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="42" customHeight="1">
       <c r="A45" s="22" t="n">
@@ -2489,16 +2778,16 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>SPGI</t>
         </is>
       </c>
       <c r="C45" s="24" t="inlineStr">
         <is>
-          <t>Omnicom Group</t>
+          <t>S&amp;P Global</t>
         </is>
       </c>
       <c r="D45" s="25" t="n">
-        <v>22.6</v>
+        <v>127.7</v>
       </c>
       <c r="E45" s="26" t="inlineStr">
         <is>
@@ -2507,12 +2796,12 @@
       </c>
       <c r="F45" s="26" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="G45" s="27" t="inlineStr">
         <is>
-          <t>+11.0</t>
+          <t>+10.9</t>
         </is>
       </c>
       <c r="H45" s="28" t="inlineStr">
@@ -2521,15 +2810,23 @@
         </is>
       </c>
       <c r="I45" s="29" t="n">
-        <v>379</v>
+        <v>91</v>
       </c>
       <c r="J45" s="30" t="inlineStr">
         <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="K45" s="31" t="inlineStr"/>
-      <c r="L45" s="31" t="inlineStr"/>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="K45" s="31" t="inlineStr">
+        <is>
+          <t>금융 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L45" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="22" t="n">
@@ -2576,8 +2873,16 @@
           <t>Information Technology</t>
         </is>
       </c>
-      <c r="K46" s="31" t="inlineStr"/>
-      <c r="L46" s="31" t="inlineStr"/>
+      <c r="K46" s="31" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L46" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="42" customHeight="1">
       <c r="A47" s="22" t="n">
@@ -2585,16 +2890,16 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>FDS</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>FactSet</t>
         </is>
       </c>
       <c r="D47" s="25" t="n">
-        <v>98.40000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E47" s="26" t="inlineStr">
         <is>
@@ -2603,12 +2908,12 @@
       </c>
       <c r="F47" s="26" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-2.2</t>
         </is>
       </c>
       <c r="G47" s="27" t="inlineStr">
         <is>
-          <t>+12.7</t>
+          <t>+11.6</t>
         </is>
       </c>
       <c r="H47" s="28" t="inlineStr">
@@ -2617,15 +2922,23 @@
         </is>
       </c>
       <c r="I47" s="29" t="n">
-        <v>118</v>
+        <v>498</v>
       </c>
       <c r="J47" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K47" s="31" t="inlineStr"/>
-      <c r="L47" s="31" t="inlineStr"/>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="K47" s="31" t="inlineStr">
+        <is>
+          <t>금융 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L47" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="42" customHeight="1">
       <c r="A48" s="22" t="n">
@@ -2633,16 +2946,16 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>FDS</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C48" s="24" t="inlineStr">
         <is>
-          <t>FactSet</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="D48" s="25" t="n">
-        <v>8.800000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="E48" s="26" t="inlineStr">
         <is>
@@ -2651,12 +2964,12 @@
       </c>
       <c r="F48" s="26" t="inlineStr">
         <is>
-          <t>-2.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="G48" s="27" t="inlineStr">
         <is>
-          <t>+11.6</t>
+          <t>+12.7</t>
         </is>
       </c>
       <c r="H48" s="28" t="inlineStr">
@@ -2665,15 +2978,23 @@
         </is>
       </c>
       <c r="I48" s="29" t="n">
-        <v>498</v>
+        <v>118</v>
       </c>
       <c r="J48" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="K48" s="31" t="inlineStr"/>
-      <c r="L48" s="31" t="inlineStr"/>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="K48" s="31" t="inlineStr">
+        <is>
+          <t>산업재·운송·방산 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L48" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="42" customHeight="1">
       <c r="A49" s="22" t="n">
@@ -2681,16 +3002,16 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>BRO</t>
         </is>
       </c>
       <c r="C49" s="24" t="inlineStr">
         <is>
-          <t>Broadridge Financial Solutions</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="D49" s="25" t="n">
-        <v>16.8</v>
+        <v>22.6</v>
       </c>
       <c r="E49" s="26" t="inlineStr">
         <is>
@@ -2699,12 +3020,12 @@
       </c>
       <c r="F49" s="26" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="G49" s="27" t="inlineStr">
         <is>
-          <t>+5.4</t>
+          <t>+12.8</t>
         </is>
       </c>
       <c r="H49" s="28" t="inlineStr">
@@ -2713,15 +3034,23 @@
         </is>
       </c>
       <c r="I49" s="29" t="n">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="J49" s="30" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="K49" s="31" t="inlineStr"/>
-      <c r="L49" s="31" t="inlineStr"/>
+          <t>Financials</t>
+        </is>
+      </c>
+      <c r="K49" s="31" t="inlineStr">
+        <is>
+          <t>금융 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L49" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="42" customHeight="1">
       <c r="A50" s="22" t="n">
@@ -2729,16 +3058,16 @@
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>BRO</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C50" s="24" t="inlineStr">
         <is>
-          <t>Brown &amp; Brown</t>
+          <t>Garmin</t>
         </is>
       </c>
       <c r="D50" s="25" t="n">
-        <v>22.6</v>
+        <v>45.6</v>
       </c>
       <c r="E50" s="26" t="inlineStr">
         <is>
@@ -2747,12 +3076,12 @@
       </c>
       <c r="F50" s="26" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="G50" s="27" t="inlineStr">
         <is>
-          <t>+12.8</t>
+          <t>+1.0</t>
         </is>
       </c>
       <c r="H50" s="28" t="inlineStr">
@@ -2761,15 +3090,23 @@
         </is>
       </c>
       <c r="I50" s="29" t="n">
-        <v>377</v>
+        <v>249</v>
       </c>
       <c r="J50" s="30" t="inlineStr">
         <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="K50" s="31" t="inlineStr"/>
-      <c r="L50" s="31" t="inlineStr"/>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="K50" s="31" t="inlineStr">
+        <is>
+          <t>소비재·자동차·레저 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L50" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="22" t="n">
@@ -2777,30 +3114,30 @@
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ROP</t>
         </is>
       </c>
       <c r="C51" s="24" t="inlineStr">
         <is>
-          <t>Garmin</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="D51" s="25" t="n">
-        <v>45.6</v>
+        <v>35.4</v>
       </c>
       <c r="E51" s="26" t="inlineStr">
         <is>
           <t>-3.3</t>
         </is>
       </c>
-      <c r="F51" s="26" t="inlineStr">
-        <is>
-          <t>-2.0</t>
+      <c r="F51" s="27" t="inlineStr">
+        <is>
+          <t>+1.2</t>
         </is>
       </c>
       <c r="G51" s="27" t="inlineStr">
         <is>
-          <t>+1.0</t>
+          <t>+6.5</t>
         </is>
       </c>
       <c r="H51" s="28" t="inlineStr">
@@ -2809,23 +3146,52 @@
         </is>
       </c>
       <c r="I51" s="29" t="n">
-        <v>249</v>
+        <v>287</v>
       </c>
       <c r="J51" s="30" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="K51" s="31" t="inlineStr"/>
-      <c r="L51" s="31" t="inlineStr"/>
-    </row>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="K51" s="31" t="inlineStr">
+        <is>
+          <t>정보기술 분야를 영위하는 미국 상장 기업</t>
+        </is>
+      </c>
+      <c r="L51" s="31" t="inlineStr">
+        <is>
+          <t>당일 전후의 종목 직접 관련 뉴스·공시 근거를 충분히 확인하지 못했습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="inlineStr">
+        <is>
+          <t>📈 금일 시황 요약 — 상승·하락 종목이 엇갈린 혼조 흐름</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="82" customHeight="1">
+      <c r="A55" s="33" t="inlineStr">
+        <is>
+          <t>관측: 상승 225개·하락 266개로 상승 비율은 46%였습니다. 강세 섹터는 Information Technology +2.5%, Energy +1.2%, 약세 섹터는 Consumer Staples -1.1%, Communication Services -1.1%였습니다. 개별 종목 중 SNDK(+14.3%)가 가장 강했고, DHR(-11.0%)가 가장 약했습니다.
+해석: 당일 전후 시황 기사 3건 이상을 검증하지 못했습니다. 아래 해석은 가격·시장 폭·섹터 수익률에 한정됩니다.
+유의: 뉴스 근거 확인이 제한된 자동 요약이며 투자 조언이 아닙니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="14">
     <mergeCell ref="C9:C10"/>
     <mergeCell ref="B9:B10"/>
+    <mergeCell ref="A54:L54"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:H9"/>
     <mergeCell ref="I9:I10"/>
+    <mergeCell ref="A55:L58"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="J9:J10"/>
